--- a/artfynd/A 26729-2025 artfynd.xlsx
+++ b/artfynd/A 26729-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888161</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26729-2025 artfynd.xlsx
+++ b/artfynd/A 26729-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888161</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26729-2025 artfynd.xlsx
+++ b/artfynd/A 26729-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888161</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26729-2025 artfynd.xlsx
+++ b/artfynd/A 26729-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888161</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26729-2025 artfynd.xlsx
+++ b/artfynd/A 26729-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888161</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
